--- a/9_Documentacion/Proyecto_CrossSelling/CrossSelling_cronograma_Agil_v1.0.xlsx
+++ b/9_Documentacion/Proyecto_CrossSelling/CrossSelling_cronograma_Agil_v1.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JOHAN\Desktop\vaope-bi\9_Documentacion\ProyectoMultiSkill\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JOHAN\Desktop\vaope-bi\9_Documentacion\Proyecto_CrossSelling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B1165B-0759-45D3-8A0F-B0CAFFB4E3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E90B18-9153-48C6-B0F1-909FAAA57EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{874EE092-DFBE-4733-8E84-3FB786537FDD}"/>
   </bookViews>
@@ -2673,6 +2673,18 @@
     <xf numFmtId="14" fontId="21" fillId="33" borderId="0" xfId="46" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2687,18 +2699,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2766,6 +2766,62 @@
         <right style="thin">
           <color rgb="FFC00000"/>
         </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -3056,24 +3112,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
@@ -3160,44 +3198,6 @@
         <bottom style="thin">
           <color theme="0" tint="-0.34998626667073579"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3311,37 +3311,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -3367,7 +3337,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border>
@@ -3378,21 +3348,33 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
       <border>
         <left/>
         <right/>
         <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3413,6 +3395,24 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -5268,28 +5268,28 @@
   <sheetData>
     <row r="2" spans="1:310" ht="25.5" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="76" t="s">
         <v>369</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
@@ -5368,36 +5368,36 @@
         <v>299</v>
       </c>
       <c r="I4" s="19"/>
-      <c r="J4" s="74" t="s">
+      <c r="J4" s="78" t="s">
         <v>300</v>
       </c>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="O4" s="75" t="s">
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="O4" s="79" t="s">
         <v>301</v>
       </c>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="T4" s="76" t="s">
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="T4" s="80" t="s">
         <v>302</v>
       </c>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="Y4" s="78" t="s">
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="Y4" s="74" t="s">
         <v>303</v>
       </c>
-      <c r="Z4" s="78"/>
-      <c r="AA4" s="78"/>
-      <c r="AB4" s="78"/>
-      <c r="AD4" s="79" t="s">
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="74"/>
+      <c r="AB4" s="74"/>
+      <c r="AD4" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="AE4" s="79"/>
-      <c r="AF4" s="79"/>
-      <c r="AG4" s="79"/>
+      <c r="AE4" s="75"/>
+      <c r="AF4" s="75"/>
+      <c r="AG4" s="75"/>
     </row>
     <row r="5" spans="1:310">
       <c r="A5" s="8"/>
@@ -5428,327 +5428,327 @@
       <c r="G6" s="20"/>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
-      <c r="J6" s="77">
+      <c r="J6" s="73">
         <v>45717</v>
       </c>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
-      <c r="V6" s="77"/>
-      <c r="W6" s="77"/>
-      <c r="X6" s="77"/>
-      <c r="Y6" s="77"/>
-      <c r="Z6" s="77"/>
-      <c r="AA6" s="77"/>
-      <c r="AB6" s="77"/>
-      <c r="AC6" s="77"/>
-      <c r="AD6" s="77"/>
-      <c r="AE6" s="77"/>
-      <c r="AF6" s="77"/>
-      <c r="AG6" s="77"/>
-      <c r="AH6" s="77"/>
-      <c r="AI6" s="77"/>
-      <c r="AJ6" s="77"/>
-      <c r="AK6" s="77"/>
-      <c r="AL6" s="77"/>
-      <c r="AM6" s="77"/>
-      <c r="AN6" s="77"/>
-      <c r="AO6" s="77">
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="73"/>
+      <c r="Z6" s="73"/>
+      <c r="AA6" s="73"/>
+      <c r="AB6" s="73"/>
+      <c r="AC6" s="73"/>
+      <c r="AD6" s="73"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="73"/>
+      <c r="AG6" s="73"/>
+      <c r="AH6" s="73"/>
+      <c r="AI6" s="73"/>
+      <c r="AJ6" s="73"/>
+      <c r="AK6" s="73"/>
+      <c r="AL6" s="73"/>
+      <c r="AM6" s="73"/>
+      <c r="AN6" s="73"/>
+      <c r="AO6" s="73">
         <v>45748</v>
       </c>
-      <c r="AP6" s="77"/>
-      <c r="AQ6" s="77"/>
-      <c r="AR6" s="77"/>
-      <c r="AS6" s="77"/>
-      <c r="AT6" s="77"/>
-      <c r="AU6" s="77"/>
-      <c r="AV6" s="77"/>
-      <c r="AW6" s="77"/>
-      <c r="AX6" s="77"/>
-      <c r="AY6" s="77"/>
-      <c r="AZ6" s="77"/>
-      <c r="BA6" s="77"/>
-      <c r="BB6" s="77"/>
-      <c r="BC6" s="77"/>
-      <c r="BD6" s="77"/>
-      <c r="BE6" s="77"/>
-      <c r="BF6" s="77"/>
-      <c r="BG6" s="77"/>
-      <c r="BH6" s="77"/>
-      <c r="BI6" s="77"/>
-      <c r="BJ6" s="77"/>
-      <c r="BK6" s="77"/>
-      <c r="BL6" s="77"/>
-      <c r="BM6" s="77"/>
-      <c r="BN6" s="77"/>
-      <c r="BO6" s="77"/>
-      <c r="BP6" s="77"/>
-      <c r="BQ6" s="77"/>
-      <c r="BR6" s="77"/>
-      <c r="BS6" s="77">
+      <c r="AP6" s="73"/>
+      <c r="AQ6" s="73"/>
+      <c r="AR6" s="73"/>
+      <c r="AS6" s="73"/>
+      <c r="AT6" s="73"/>
+      <c r="AU6" s="73"/>
+      <c r="AV6" s="73"/>
+      <c r="AW6" s="73"/>
+      <c r="AX6" s="73"/>
+      <c r="AY6" s="73"/>
+      <c r="AZ6" s="73"/>
+      <c r="BA6" s="73"/>
+      <c r="BB6" s="73"/>
+      <c r="BC6" s="73"/>
+      <c r="BD6" s="73"/>
+      <c r="BE6" s="73"/>
+      <c r="BF6" s="73"/>
+      <c r="BG6" s="73"/>
+      <c r="BH6" s="73"/>
+      <c r="BI6" s="73"/>
+      <c r="BJ6" s="73"/>
+      <c r="BK6" s="73"/>
+      <c r="BL6" s="73"/>
+      <c r="BM6" s="73"/>
+      <c r="BN6" s="73"/>
+      <c r="BO6" s="73"/>
+      <c r="BP6" s="73"/>
+      <c r="BQ6" s="73"/>
+      <c r="BR6" s="73"/>
+      <c r="BS6" s="73">
         <v>45778</v>
       </c>
-      <c r="BT6" s="77"/>
-      <c r="BU6" s="77"/>
-      <c r="BV6" s="77"/>
-      <c r="BW6" s="77"/>
-      <c r="BX6" s="77"/>
-      <c r="BY6" s="77"/>
-      <c r="BZ6" s="77"/>
-      <c r="CA6" s="77"/>
-      <c r="CB6" s="77"/>
-      <c r="CC6" s="77"/>
-      <c r="CD6" s="77"/>
-      <c r="CE6" s="77"/>
-      <c r="CF6" s="77"/>
-      <c r="CG6" s="77"/>
-      <c r="CH6" s="77"/>
-      <c r="CI6" s="77"/>
-      <c r="CJ6" s="77"/>
-      <c r="CK6" s="77"/>
-      <c r="CL6" s="77"/>
-      <c r="CM6" s="77"/>
-      <c r="CN6" s="77"/>
-      <c r="CO6" s="77"/>
-      <c r="CP6" s="77"/>
-      <c r="CQ6" s="77"/>
-      <c r="CR6" s="77"/>
-      <c r="CS6" s="77"/>
-      <c r="CT6" s="77"/>
-      <c r="CU6" s="77"/>
-      <c r="CV6" s="77"/>
-      <c r="CW6" s="77"/>
-      <c r="CX6" s="77">
+      <c r="BT6" s="73"/>
+      <c r="BU6" s="73"/>
+      <c r="BV6" s="73"/>
+      <c r="BW6" s="73"/>
+      <c r="BX6" s="73"/>
+      <c r="BY6" s="73"/>
+      <c r="BZ6" s="73"/>
+      <c r="CA6" s="73"/>
+      <c r="CB6" s="73"/>
+      <c r="CC6" s="73"/>
+      <c r="CD6" s="73"/>
+      <c r="CE6" s="73"/>
+      <c r="CF6" s="73"/>
+      <c r="CG6" s="73"/>
+      <c r="CH6" s="73"/>
+      <c r="CI6" s="73"/>
+      <c r="CJ6" s="73"/>
+      <c r="CK6" s="73"/>
+      <c r="CL6" s="73"/>
+      <c r="CM6" s="73"/>
+      <c r="CN6" s="73"/>
+      <c r="CO6" s="73"/>
+      <c r="CP6" s="73"/>
+      <c r="CQ6" s="73"/>
+      <c r="CR6" s="73"/>
+      <c r="CS6" s="73"/>
+      <c r="CT6" s="73"/>
+      <c r="CU6" s="73"/>
+      <c r="CV6" s="73"/>
+      <c r="CW6" s="73"/>
+      <c r="CX6" s="73">
         <v>45809</v>
       </c>
-      <c r="CY6" s="77"/>
-      <c r="CZ6" s="77"/>
-      <c r="DA6" s="77"/>
-      <c r="DB6" s="77"/>
-      <c r="DC6" s="77"/>
-      <c r="DD6" s="77"/>
-      <c r="DE6" s="77"/>
-      <c r="DF6" s="77"/>
-      <c r="DG6" s="77"/>
-      <c r="DH6" s="77"/>
-      <c r="DI6" s="77"/>
-      <c r="DJ6" s="77"/>
-      <c r="DK6" s="77"/>
-      <c r="DL6" s="77"/>
-      <c r="DM6" s="77"/>
-      <c r="DN6" s="77"/>
-      <c r="DO6" s="77"/>
-      <c r="DP6" s="77"/>
-      <c r="DQ6" s="77"/>
-      <c r="DR6" s="77"/>
-      <c r="DS6" s="77"/>
-      <c r="DT6" s="77"/>
-      <c r="DU6" s="77"/>
-      <c r="DV6" s="77"/>
-      <c r="DW6" s="77"/>
-      <c r="DX6" s="77"/>
-      <c r="DY6" s="77"/>
-      <c r="DZ6" s="77"/>
-      <c r="EA6" s="77"/>
-      <c r="EB6" s="77">
+      <c r="CY6" s="73"/>
+      <c r="CZ6" s="73"/>
+      <c r="DA6" s="73"/>
+      <c r="DB6" s="73"/>
+      <c r="DC6" s="73"/>
+      <c r="DD6" s="73"/>
+      <c r="DE6" s="73"/>
+      <c r="DF6" s="73"/>
+      <c r="DG6" s="73"/>
+      <c r="DH6" s="73"/>
+      <c r="DI6" s="73"/>
+      <c r="DJ6" s="73"/>
+      <c r="DK6" s="73"/>
+      <c r="DL6" s="73"/>
+      <c r="DM6" s="73"/>
+      <c r="DN6" s="73"/>
+      <c r="DO6" s="73"/>
+      <c r="DP6" s="73"/>
+      <c r="DQ6" s="73"/>
+      <c r="DR6" s="73"/>
+      <c r="DS6" s="73"/>
+      <c r="DT6" s="73"/>
+      <c r="DU6" s="73"/>
+      <c r="DV6" s="73"/>
+      <c r="DW6" s="73"/>
+      <c r="DX6" s="73"/>
+      <c r="DY6" s="73"/>
+      <c r="DZ6" s="73"/>
+      <c r="EA6" s="73"/>
+      <c r="EB6" s="73">
         <v>45839</v>
       </c>
-      <c r="EC6" s="77"/>
-      <c r="ED6" s="77"/>
-      <c r="EE6" s="77"/>
-      <c r="EF6" s="77"/>
-      <c r="EG6" s="77"/>
-      <c r="EH6" s="77"/>
-      <c r="EI6" s="77"/>
-      <c r="EJ6" s="77"/>
-      <c r="EK6" s="77"/>
-      <c r="EL6" s="77"/>
-      <c r="EM6" s="77"/>
-      <c r="EN6" s="77"/>
-      <c r="EO6" s="77"/>
-      <c r="EP6" s="77"/>
-      <c r="EQ6" s="77"/>
-      <c r="ER6" s="77"/>
-      <c r="ES6" s="77"/>
-      <c r="ET6" s="77"/>
-      <c r="EU6" s="77"/>
-      <c r="EV6" s="77"/>
-      <c r="EW6" s="77"/>
-      <c r="EX6" s="77"/>
-      <c r="EY6" s="77"/>
-      <c r="EZ6" s="77"/>
-      <c r="FA6" s="77"/>
-      <c r="FB6" s="77"/>
-      <c r="FC6" s="77"/>
-      <c r="FD6" s="77"/>
-      <c r="FE6" s="77"/>
-      <c r="FF6" s="77"/>
-      <c r="FG6" s="77">
+      <c r="EC6" s="73"/>
+      <c r="ED6" s="73"/>
+      <c r="EE6" s="73"/>
+      <c r="EF6" s="73"/>
+      <c r="EG6" s="73"/>
+      <c r="EH6" s="73"/>
+      <c r="EI6" s="73"/>
+      <c r="EJ6" s="73"/>
+      <c r="EK6" s="73"/>
+      <c r="EL6" s="73"/>
+      <c r="EM6" s="73"/>
+      <c r="EN6" s="73"/>
+      <c r="EO6" s="73"/>
+      <c r="EP6" s="73"/>
+      <c r="EQ6" s="73"/>
+      <c r="ER6" s="73"/>
+      <c r="ES6" s="73"/>
+      <c r="ET6" s="73"/>
+      <c r="EU6" s="73"/>
+      <c r="EV6" s="73"/>
+      <c r="EW6" s="73"/>
+      <c r="EX6" s="73"/>
+      <c r="EY6" s="73"/>
+      <c r="EZ6" s="73"/>
+      <c r="FA6" s="73"/>
+      <c r="FB6" s="73"/>
+      <c r="FC6" s="73"/>
+      <c r="FD6" s="73"/>
+      <c r="FE6" s="73"/>
+      <c r="FF6" s="73"/>
+      <c r="FG6" s="73">
         <v>45870</v>
       </c>
-      <c r="FH6" s="77"/>
-      <c r="FI6" s="77"/>
-      <c r="FJ6" s="77"/>
-      <c r="FK6" s="77"/>
-      <c r="FL6" s="77"/>
-      <c r="FM6" s="77"/>
-      <c r="FN6" s="77"/>
-      <c r="FO6" s="77"/>
-      <c r="FP6" s="77"/>
-      <c r="FQ6" s="77"/>
-      <c r="FR6" s="77"/>
-      <c r="FS6" s="77"/>
-      <c r="FT6" s="77"/>
-      <c r="FU6" s="77"/>
-      <c r="FV6" s="77"/>
-      <c r="FW6" s="77"/>
-      <c r="FX6" s="77"/>
-      <c r="FY6" s="77"/>
-      <c r="FZ6" s="77"/>
-      <c r="GA6" s="77"/>
-      <c r="GB6" s="77"/>
-      <c r="GC6" s="77"/>
-      <c r="GD6" s="77"/>
-      <c r="GE6" s="77"/>
-      <c r="GF6" s="77"/>
-      <c r="GG6" s="77"/>
-      <c r="GH6" s="77"/>
-      <c r="GI6" s="77"/>
-      <c r="GJ6" s="77"/>
-      <c r="GK6" s="77"/>
-      <c r="GL6" s="77">
+      <c r="FH6" s="73"/>
+      <c r="FI6" s="73"/>
+      <c r="FJ6" s="73"/>
+      <c r="FK6" s="73"/>
+      <c r="FL6" s="73"/>
+      <c r="FM6" s="73"/>
+      <c r="FN6" s="73"/>
+      <c r="FO6" s="73"/>
+      <c r="FP6" s="73"/>
+      <c r="FQ6" s="73"/>
+      <c r="FR6" s="73"/>
+      <c r="FS6" s="73"/>
+      <c r="FT6" s="73"/>
+      <c r="FU6" s="73"/>
+      <c r="FV6" s="73"/>
+      <c r="FW6" s="73"/>
+      <c r="FX6" s="73"/>
+      <c r="FY6" s="73"/>
+      <c r="FZ6" s="73"/>
+      <c r="GA6" s="73"/>
+      <c r="GB6" s="73"/>
+      <c r="GC6" s="73"/>
+      <c r="GD6" s="73"/>
+      <c r="GE6" s="73"/>
+      <c r="GF6" s="73"/>
+      <c r="GG6" s="73"/>
+      <c r="GH6" s="73"/>
+      <c r="GI6" s="73"/>
+      <c r="GJ6" s="73"/>
+      <c r="GK6" s="73"/>
+      <c r="GL6" s="73">
         <v>45901</v>
       </c>
-      <c r="GM6" s="77"/>
-      <c r="GN6" s="77"/>
-      <c r="GO6" s="77"/>
-      <c r="GP6" s="77"/>
-      <c r="GQ6" s="77"/>
-      <c r="GR6" s="77"/>
-      <c r="GS6" s="77"/>
-      <c r="GT6" s="77"/>
-      <c r="GU6" s="77"/>
-      <c r="GV6" s="77"/>
-      <c r="GW6" s="77"/>
-      <c r="GX6" s="77"/>
-      <c r="GY6" s="77"/>
-      <c r="GZ6" s="77"/>
-      <c r="HA6" s="77"/>
-      <c r="HB6" s="77"/>
-      <c r="HC6" s="77"/>
-      <c r="HD6" s="77"/>
-      <c r="HE6" s="77"/>
-      <c r="HF6" s="77"/>
-      <c r="HG6" s="77"/>
-      <c r="HH6" s="77"/>
-      <c r="HI6" s="77"/>
-      <c r="HJ6" s="77"/>
-      <c r="HK6" s="77"/>
-      <c r="HL6" s="77">
+      <c r="GM6" s="73"/>
+      <c r="GN6" s="73"/>
+      <c r="GO6" s="73"/>
+      <c r="GP6" s="73"/>
+      <c r="GQ6" s="73"/>
+      <c r="GR6" s="73"/>
+      <c r="GS6" s="73"/>
+      <c r="GT6" s="73"/>
+      <c r="GU6" s="73"/>
+      <c r="GV6" s="73"/>
+      <c r="GW6" s="73"/>
+      <c r="GX6" s="73"/>
+      <c r="GY6" s="73"/>
+      <c r="GZ6" s="73"/>
+      <c r="HA6" s="73"/>
+      <c r="HB6" s="73"/>
+      <c r="HC6" s="73"/>
+      <c r="HD6" s="73"/>
+      <c r="HE6" s="73"/>
+      <c r="HF6" s="73"/>
+      <c r="HG6" s="73"/>
+      <c r="HH6" s="73"/>
+      <c r="HI6" s="73"/>
+      <c r="HJ6" s="73"/>
+      <c r="HK6" s="73"/>
+      <c r="HL6" s="73">
         <v>45931</v>
       </c>
-      <c r="HM6" s="77"/>
-      <c r="HN6" s="77"/>
-      <c r="HO6" s="77"/>
-      <c r="HP6" s="77"/>
-      <c r="HQ6" s="77"/>
-      <c r="HR6" s="77"/>
-      <c r="HS6" s="77"/>
-      <c r="HT6" s="77"/>
-      <c r="HU6" s="77"/>
-      <c r="HV6" s="77"/>
-      <c r="HW6" s="77"/>
-      <c r="HX6" s="77"/>
-      <c r="HY6" s="77"/>
-      <c r="HZ6" s="77"/>
-      <c r="IA6" s="77"/>
-      <c r="IB6" s="77"/>
-      <c r="IC6" s="77"/>
-      <c r="ID6" s="77"/>
-      <c r="IE6" s="77"/>
-      <c r="IF6" s="77"/>
-      <c r="IG6" s="77"/>
-      <c r="IH6" s="77"/>
-      <c r="II6" s="77"/>
-      <c r="IJ6" s="77"/>
-      <c r="IK6" s="77"/>
-      <c r="IL6" s="77"/>
-      <c r="IM6" s="77"/>
-      <c r="IN6" s="77"/>
-      <c r="IO6" s="77"/>
-      <c r="IP6" s="77"/>
-      <c r="IQ6" s="77">
+      <c r="HM6" s="73"/>
+      <c r="HN6" s="73"/>
+      <c r="HO6" s="73"/>
+      <c r="HP6" s="73"/>
+      <c r="HQ6" s="73"/>
+      <c r="HR6" s="73"/>
+      <c r="HS6" s="73"/>
+      <c r="HT6" s="73"/>
+      <c r="HU6" s="73"/>
+      <c r="HV6" s="73"/>
+      <c r="HW6" s="73"/>
+      <c r="HX6" s="73"/>
+      <c r="HY6" s="73"/>
+      <c r="HZ6" s="73"/>
+      <c r="IA6" s="73"/>
+      <c r="IB6" s="73"/>
+      <c r="IC6" s="73"/>
+      <c r="ID6" s="73"/>
+      <c r="IE6" s="73"/>
+      <c r="IF6" s="73"/>
+      <c r="IG6" s="73"/>
+      <c r="IH6" s="73"/>
+      <c r="II6" s="73"/>
+      <c r="IJ6" s="73"/>
+      <c r="IK6" s="73"/>
+      <c r="IL6" s="73"/>
+      <c r="IM6" s="73"/>
+      <c r="IN6" s="73"/>
+      <c r="IO6" s="73"/>
+      <c r="IP6" s="73"/>
+      <c r="IQ6" s="73">
         <v>45962</v>
       </c>
-      <c r="IR6" s="77"/>
-      <c r="IS6" s="77"/>
-      <c r="IT6" s="77"/>
-      <c r="IU6" s="77"/>
-      <c r="IV6" s="77"/>
-      <c r="IW6" s="77"/>
-      <c r="IX6" s="77"/>
-      <c r="IY6" s="77"/>
-      <c r="IZ6" s="77"/>
-      <c r="JA6" s="77"/>
-      <c r="JB6" s="77"/>
-      <c r="JC6" s="77"/>
-      <c r="JD6" s="77"/>
-      <c r="JE6" s="77"/>
-      <c r="JF6" s="77"/>
-      <c r="JG6" s="77"/>
-      <c r="JH6" s="77"/>
-      <c r="JI6" s="77"/>
-      <c r="JJ6" s="77"/>
-      <c r="JK6" s="77"/>
-      <c r="JL6" s="77"/>
-      <c r="JM6" s="77"/>
-      <c r="JN6" s="77"/>
-      <c r="JO6" s="77"/>
-      <c r="JP6" s="77"/>
-      <c r="JQ6" s="77"/>
-      <c r="JR6" s="77"/>
-      <c r="JS6" s="77"/>
-      <c r="JT6" s="77"/>
-      <c r="JU6" s="77"/>
-      <c r="JV6" s="77">
+      <c r="IR6" s="73"/>
+      <c r="IS6" s="73"/>
+      <c r="IT6" s="73"/>
+      <c r="IU6" s="73"/>
+      <c r="IV6" s="73"/>
+      <c r="IW6" s="73"/>
+      <c r="IX6" s="73"/>
+      <c r="IY6" s="73"/>
+      <c r="IZ6" s="73"/>
+      <c r="JA6" s="73"/>
+      <c r="JB6" s="73"/>
+      <c r="JC6" s="73"/>
+      <c r="JD6" s="73"/>
+      <c r="JE6" s="73"/>
+      <c r="JF6" s="73"/>
+      <c r="JG6" s="73"/>
+      <c r="JH6" s="73"/>
+      <c r="JI6" s="73"/>
+      <c r="JJ6" s="73"/>
+      <c r="JK6" s="73"/>
+      <c r="JL6" s="73"/>
+      <c r="JM6" s="73"/>
+      <c r="JN6" s="73"/>
+      <c r="JO6" s="73"/>
+      <c r="JP6" s="73"/>
+      <c r="JQ6" s="73"/>
+      <c r="JR6" s="73"/>
+      <c r="JS6" s="73"/>
+      <c r="JT6" s="73"/>
+      <c r="JU6" s="73"/>
+      <c r="JV6" s="73">
         <v>45992</v>
       </c>
-      <c r="JW6" s="77"/>
-      <c r="JX6" s="77"/>
-      <c r="JY6" s="77"/>
-      <c r="JZ6" s="77"/>
-      <c r="KA6" s="77"/>
-      <c r="KB6" s="77"/>
-      <c r="KC6" s="77"/>
-      <c r="KD6" s="77"/>
-      <c r="KE6" s="77"/>
-      <c r="KF6" s="77"/>
-      <c r="KG6" s="77"/>
-      <c r="KH6" s="77"/>
-      <c r="KI6" s="77"/>
-      <c r="KJ6" s="77"/>
-      <c r="KK6" s="77"/>
-      <c r="KL6" s="77"/>
-      <c r="KM6" s="77"/>
-      <c r="KN6" s="77"/>
-      <c r="KO6" s="77"/>
-      <c r="KP6" s="77"/>
-      <c r="KQ6" s="77"/>
-      <c r="KR6" s="77"/>
-      <c r="KS6" s="77"/>
-      <c r="KT6" s="77"/>
-      <c r="KU6" s="77"/>
-      <c r="KV6" s="77"/>
-      <c r="KW6" s="77"/>
-      <c r="KX6" s="77"/>
+      <c r="JW6" s="73"/>
+      <c r="JX6" s="73"/>
+      <c r="JY6" s="73"/>
+      <c r="JZ6" s="73"/>
+      <c r="KA6" s="73"/>
+      <c r="KB6" s="73"/>
+      <c r="KC6" s="73"/>
+      <c r="KD6" s="73"/>
+      <c r="KE6" s="73"/>
+      <c r="KF6" s="73"/>
+      <c r="KG6" s="73"/>
+      <c r="KH6" s="73"/>
+      <c r="KI6" s="73"/>
+      <c r="KJ6" s="73"/>
+      <c r="KK6" s="73"/>
+      <c r="KL6" s="73"/>
+      <c r="KM6" s="73"/>
+      <c r="KN6" s="73"/>
+      <c r="KO6" s="73"/>
+      <c r="KP6" s="73"/>
+      <c r="KQ6" s="73"/>
+      <c r="KR6" s="73"/>
+      <c r="KS6" s="73"/>
+      <c r="KT6" s="73"/>
+      <c r="KU6" s="73"/>
+      <c r="KV6" s="73"/>
+      <c r="KW6" s="73"/>
+      <c r="KX6" s="73"/>
     </row>
     <row r="7" spans="1:310">
       <c r="A7" s="8"/>
@@ -15788,7 +15788,7 @@
         <v>358</v>
       </c>
       <c r="E33" s="54">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F33" s="71">
         <v>46064</v>
@@ -15808,7 +15808,7 @@
       <c r="C34" s="53" t="s">
         <v>300</v>
       </c>
-      <c r="D34" s="80" t="s">
+      <c r="D34" s="72" t="s">
         <v>315</v>
       </c>
       <c r="E34" s="54">
@@ -15865,6 +15865,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="T4:W4"/>
     <mergeCell ref="JV6:KX6"/>
     <mergeCell ref="Y4:AB4"/>
     <mergeCell ref="AD4:AG4"/>
@@ -15877,12 +15883,6 @@
     <mergeCell ref="GL6:HK6"/>
     <mergeCell ref="HL6:IP6"/>
     <mergeCell ref="IQ6:JU6"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="T4:W4"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E36">
     <cfRule type="dataBar" priority="41">
@@ -15899,28 +15899,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="expression" dxfId="36" priority="39">
+    <cfRule type="expression" dxfId="36" priority="40">
+      <formula>J$7&lt;=EOMONTH($J$7,0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="39">
       <formula>AND(J$7&lt;=EOMONTH($J$7,1),J$7&gt;EOMONTH($J$7,0))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="40">
-      <formula>J$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J10:BM12 DA10:FD12 J13:KX28">
-    <cfRule type="expression" dxfId="34" priority="123" stopIfTrue="1">
-      <formula>AND($C10="Riesgo bajo",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
+    <cfRule type="expression" dxfId="34" priority="127" stopIfTrue="1">
+      <formula>AND(LEN($C10)=0,J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="124" stopIfTrue="1">
-      <formula>AND($C10="Riesgo alto",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
+    <cfRule type="expression" dxfId="33" priority="126" stopIfTrue="1">
+      <formula>AND($C10="Riesgo medio",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="32" priority="125" stopIfTrue="1">
       <formula>AND($C10="Según lo previsto",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="126" stopIfTrue="1">
-      <formula>AND($C10="Riesgo medio",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
+    <cfRule type="expression" dxfId="31" priority="124" stopIfTrue="1">
+      <formula>AND($C10="Riesgo alto",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="127" stopIfTrue="1">
-      <formula>AND(LEN($C10)=0,J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
+    <cfRule type="expression" dxfId="30" priority="123" stopIfTrue="1">
+      <formula>AND($C10="Riesgo bajo",J$7&gt;=$F10,J$7&lt;=$F10+$H10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:KW9 J10:BL12 DA10:FC12 J13:KW28">
@@ -15929,14 +15929,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO6">
-    <cfRule type="expression" dxfId="28" priority="25">
-      <formula>AP$7&lt;=EOMONTH($J$7,0)</formula>
+    <cfRule type="expression" dxfId="28" priority="27">
+      <formula>AND(AP$7&lt;=EOMONTH($J$7,2),AP$7&gt;EOMONTH($J$7,0),AP$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="27" priority="26">
       <formula>AND(AP$7&lt;=EOMONTH($J$7,1),AP$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="27">
-      <formula>AND(AP$7&lt;=EOMONTH($J$7,2),AP$7&gt;EOMONTH($J$7,0),AP$7&gt;EOMONTH($J$7,1))</formula>
+    <cfRule type="expression" dxfId="26" priority="25">
+      <formula>AP$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM10:BM12 FD10:FD12 KX13:KX28">
@@ -15948,88 +15948,88 @@
     <cfRule type="expression" dxfId="24" priority="22">
       <formula>BT$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="23" priority="24">
+      <formula>AND(BT$7&lt;=EOMONTH($J$7,2),BT$7&gt;EOMONTH($J$7,0),BT$7&gt;EOMONTH($J$7,1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="23">
       <formula>AND(BT$7&lt;=EOMONTH($J$7,1),BT$7&gt;EOMONTH($J$7,0))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="24">
-      <formula>AND(BT$7&lt;=EOMONTH($J$7,2),BT$7&gt;EOMONTH($J$7,0),BT$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX6">
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="21" priority="21">
+      <formula>AND(CY$7&lt;=EOMONTH($J$7,2),CY$7&gt;EOMONTH($J$7,0),CY$7&gt;EOMONTH($J$7,1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>CY$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>AND(CY$7&lt;=EOMONTH($J$7,1),CY$7&gt;EOMONTH($J$7,0))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="21">
-      <formula>AND(CY$7&lt;=EOMONTH($J$7,2),CY$7&gt;EOMONTH($J$7,0),CY$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EB6">
-    <cfRule type="expression" dxfId="18" priority="16">
-      <formula>EC$7&lt;=EOMONTH($J$7,0)</formula>
+    <cfRule type="expression" dxfId="18" priority="18">
+      <formula>AND(EC$7&lt;=EOMONTH($J$7,2),EC$7&gt;EOMONTH($J$7,0),EC$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="17">
       <formula>AND(EC$7&lt;=EOMONTH($J$7,1),EC$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>AND(EC$7&lt;=EOMONTH($J$7,2),EC$7&gt;EOMONTH($J$7,0),EC$7&gt;EOMONTH($J$7,1))</formula>
+    <cfRule type="expression" dxfId="16" priority="16">
+      <formula>EC$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FG6">
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>FH$7&lt;=EOMONTH($J$7,0)</formula>
+    <cfRule type="expression" dxfId="15" priority="15">
+      <formula>AND(FH$7&lt;=EOMONTH($J$7,2),FH$7&gt;EOMONTH($J$7,0),FH$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="14">
       <formula>AND(FH$7&lt;=EOMONTH($J$7,1),FH$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15">
-      <formula>AND(FH$7&lt;=EOMONTH($J$7,2),FH$7&gt;EOMONTH($J$7,0),FH$7&gt;EOMONTH($J$7,1))</formula>
+    <cfRule type="expression" dxfId="13" priority="13">
+      <formula>FH$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GL6">
-    <cfRule type="expression" dxfId="12" priority="10">
-      <formula>GM$7&lt;=EOMONTH($J$7,0)</formula>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>AND(GM$7&lt;=EOMONTH($J$7,2),GM$7&gt;EOMONTH($J$7,0),GM$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="11">
       <formula>AND(GM$7&lt;=EOMONTH($J$7,1),GM$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="12">
-      <formula>AND(GM$7&lt;=EOMONTH($J$7,2),GM$7&gt;EOMONTH($J$7,0),GM$7&gt;EOMONTH($J$7,1))</formula>
+    <cfRule type="expression" dxfId="10" priority="10">
+      <formula>GM$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="HL6">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>HM$7&lt;=EOMONTH($J$7,0)</formula>
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND(HM$7&lt;=EOMONTH($J$7,2),HM$7&gt;EOMONTH($J$7,0),HM$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="8">
       <formula>AND(HM$7&lt;=EOMONTH($J$7,1),HM$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="9">
-      <formula>AND(HM$7&lt;=EOMONTH($J$7,2),HM$7&gt;EOMONTH($J$7,0),HM$7&gt;EOMONTH($J$7,1))</formula>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>HM$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="IQ6">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>IR$7&lt;=EOMONTH($J$7,0)</formula>
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>AND(IR$7&lt;=EOMONTH($J$7,2),IR$7&gt;EOMONTH($J$7,0),IR$7&gt;EOMONTH($J$7,1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="5">
       <formula>AND(IR$7&lt;=EOMONTH($J$7,1),IR$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>AND(IR$7&lt;=EOMONTH($J$7,2),IR$7&gt;EOMONTH($J$7,0),IR$7&gt;EOMONTH($J$7,1))</formula>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>IR$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="JV6">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>JW$7&lt;=EOMONTH($J$7,0)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(JW$7&lt;=EOMONTH($J$7,1),JW$7&gt;EOMONTH($J$7,0))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND(JW$7&lt;=EOMONTH($J$7,2),JW$7&gt;EOMONTH($J$7,0),JW$7&gt;EOMONTH($J$7,1))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>JW$7&lt;=EOMONTH($J$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="KX7:KX9">
